--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCION 100/LTAIPT_A63F100.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCION 100/LTAIPT_A63F100.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="495" windowWidth="19815" windowHeight="9405"/>
+    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -109,28 +109,28 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2022</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
-    <t>F579353CA8CFE5EEF234B361084C6382</t>
-  </si>
-  <si>
-    <t>01/04/2022</t>
-  </si>
-  <si>
-    <t>30/06/2022</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202022/Area_de_Transparencia/Tabla%20de%20Aplicabilidad/TABLA%20DE%20APLICABILIDAD%202022.pdf</t>
-  </si>
-  <si>
-    <t>Transparencia y Archivo</t>
-  </si>
-  <si>
-    <t>11/07/2022</t>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Area_de_Transparencia/Tabla%20de%20Aplicabilidad/Tabla%20de%20Aplicabilidad.pdf</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>66494DC304CBF9711F5086F9DBF0DF8A</t>
+  </si>
+  <si>
+    <t>01/04/2023</t>
+  </si>
+  <si>
+    <t>30/06/2023</t>
+  </si>
+  <si>
+    <t>Área de Transparencia</t>
+  </si>
+  <si>
+    <t>10/07/2023</t>
   </si>
 </sst>
 </file>
@@ -526,7 +526,7 @@
   <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.5703125" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="35.7109375" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -677,22 +677,22 @@
     </row>
     <row r="8" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>37</v>
@@ -704,7 +704,7 @@
         <v>38</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
